--- a/WEB-ScSc/ExcelExamples/Hebrew-עברית.xlsx
+++ b/WEB-ScSc/ExcelExamples/Hebrew-עברית.xlsx
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>מערכת סיטרין</t>
+          <t>מערכת ימ סוףט</t>
         </is>
       </c>
     </row>
@@ -1113,42 +1113,6 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>יום ראשון, יום שני, יום שלישי, יום רביעי, יום חמישי, יום שישי</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>LANGUAGES_LIST</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>English,Hebrew,Russian</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>app_size</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1500x900</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>unavailable_slot</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>XXXXXXXX</t>
         </is>
       </c>
     </row>
